--- a/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20231201_20240601.xlsx
+++ b/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20231201_20240601.xlsx
@@ -921,37 +921,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60.16260162601627</v>
+        <v>58.53658536585365</v>
       </c>
       <c r="C12" t="n">
-        <v>39.83739837398374</v>
+        <v>40.65040650406504</v>
       </c>
       <c r="D12" t="n">
-        <v>65.31002452492545</v>
+        <v>82.59896609664953</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>INE226A01021</t>
+          <t>INE274J01014</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G12" t="n">
-        <v>-20.32520325203253</v>
+        <v>-17.88617886178861</v>
       </c>
       <c r="H12" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I12" t="n">
         <v>56</v>
       </c>
       <c r="J12" t="n">
-        <v>1359.7</v>
+        <v>423.8</v>
       </c>
       <c r="K12" t="n">
         <v>11</v>
@@ -965,37 +965,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>63.41463414634146</v>
+        <v>60.16260162601627</v>
       </c>
       <c r="C13" t="n">
-        <v>35.77235772357724</v>
+        <v>39.83739837398374</v>
       </c>
       <c r="D13" t="n">
-        <v>55.83575828253289</v>
+        <v>65.31002452492545</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>INE257A01026</t>
+          <t>INE226A01021</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="G13" t="n">
-        <v>-27.64227642276423</v>
+        <v>-20.32520325203253</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I13" t="n">
         <v>56</v>
       </c>
       <c r="J13" t="n">
-        <v>298.9</v>
+        <v>1359.7</v>
       </c>
       <c r="K13" t="n">
         <v>12</v>
@@ -1009,37 +1009,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>58.53658536585365</v>
+        <v>63.41463414634146</v>
       </c>
       <c r="C14" t="n">
-        <v>40.65040650406504</v>
+        <v>35.77235772357724</v>
       </c>
       <c r="D14" t="n">
-        <v>82.59896609664953</v>
+        <v>55.83575828253289</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>INE274J01014</t>
+          <t>INE257A01026</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="G14" t="n">
-        <v>-17.88617886178861</v>
+        <v>-27.64227642276423</v>
       </c>
       <c r="H14" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
         <v>56</v>
       </c>
       <c r="J14" t="n">
-        <v>423.8</v>
+        <v>298.9</v>
       </c>
       <c r="K14" t="n">
         <v>13</v>
